--- a/pa-temp-fix-system.com/php/shell/sp/product/excel/M4-M6 关停清单v3.xlsx
+++ b/pa-temp-fix-system.com/php/shell/sp/product/excel/M4-M6 关停清单v3.xlsx
@@ -1201,7 +1201,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:C122"/>
   <sheetFormatPr defaultColWidth="8.88461538461539" defaultRowHeight="16.8" outlineLevelCol="2"/>
   <cols>
@@ -1221,7 +1221,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" hidden="1" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>426346349770645</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" hidden="1" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>323856733573761</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" hidden="1" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -1254,7 +1254,7 @@
         <v>370915358032519</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" hidden="1" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>356496521070463</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" hidden="1" spans="1:3">
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>311366409564048</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" hidden="1" spans="1:3">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>538526667312500</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" hidden="1" spans="1:3">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>434196027126914</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" hidden="1" spans="1:3">
       <c r="A10" s="1" t="s">
         <v>3</v>
       </c>
@@ -1320,7 +1320,7 @@
         <v>325865606214463</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" hidden="1" spans="1:3">
       <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
@@ -1331,7 +1331,7 @@
         <v>425696896260291</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" hidden="1" spans="1:3">
       <c r="A12" s="1" t="s">
         <v>3</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>493659458196741</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" hidden="1" spans="1:3">
       <c r="A13" s="1" t="s">
         <v>3</v>
       </c>
@@ -1353,7 +1353,7 @@
         <v>480770648462827</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" hidden="1" spans="1:3">
       <c r="A14" s="1" t="s">
         <v>3</v>
       </c>
@@ -1364,7 +1364,7 @@
         <v>435546092669778</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" hidden="1" spans="1:3">
       <c r="A15" s="1" t="s">
         <v>3</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>283086032379351</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" hidden="1" spans="1:3">
       <c r="A16" s="1" t="s">
         <v>3</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>549755812647130</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" hidden="1" spans="1:3">
       <c r="A17" s="1" t="s">
         <v>3</v>
       </c>
@@ -1397,7 +1397,7 @@
         <v>324323648712320</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" hidden="1" spans="1:3">
       <c r="A18" s="1" t="s">
         <v>3</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>453740064231728</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" hidden="1" spans="1:3">
       <c r="A19" s="1" t="s">
         <v>3</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>468196057681704</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" hidden="1" spans="1:3">
       <c r="A20" s="1" t="s">
         <v>3</v>
       </c>
@@ -1430,7 +1430,7 @@
         <v>536279817656829</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" hidden="1" spans="1:3">
       <c r="A21" s="1" t="s">
         <v>3</v>
       </c>
@@ -1441,7 +1441,7 @@
         <v>334150973458366</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" hidden="1" spans="1:3">
       <c r="A22" s="1" t="s">
         <v>3</v>
       </c>
@@ -1452,7 +1452,7 @@
         <v>531406907224312</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" hidden="1" spans="1:3">
       <c r="A23" s="1" t="s">
         <v>3</v>
       </c>
@@ -1463,7 +1463,7 @@
         <v>371515449475533</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" hidden="1" spans="1:3">
       <c r="A24" s="1" t="s">
         <v>3</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>354879242024700</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" hidden="1" spans="1:3">
       <c r="A25" s="1" t="s">
         <v>3</v>
       </c>
@@ -1485,7 +1485,7 @@
         <v>369585446810363</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" hidden="1" spans="1:3">
       <c r="A26" s="1" t="s">
         <v>3</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>350255086472896</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" hidden="1" spans="1:3">
       <c r="A27" s="1" t="s">
         <v>3</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>433668248414859</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" hidden="1" spans="1:3">
       <c r="A28" s="1" t="s">
         <v>3</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>518325603364536</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" hidden="1" spans="1:3">
       <c r="A29" s="1" t="s">
         <v>3</v>
       </c>
@@ -1529,7 +1529,7 @@
         <v>346730470815140</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" hidden="1" spans="1:3">
       <c r="A30" s="1" t="s">
         <v>3</v>
       </c>
@@ -1540,7 +1540,7 @@
         <v>550201009589247</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" hidden="1" spans="1:3">
       <c r="A31" s="1" t="s">
         <v>3</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>466137148642095</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" hidden="1" spans="1:3">
       <c r="A32" s="1" t="s">
         <v>3</v>
       </c>
@@ -1562,7 +1562,7 @@
         <v>329531763465578</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" hidden="1" spans="1:3">
       <c r="A33" s="1" t="s">
         <v>3</v>
       </c>
@@ -1573,7 +1573,7 @@
         <v>324801115947548</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" hidden="1" spans="1:3">
       <c r="A34" s="1" t="s">
         <v>3</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>310904778352873</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" hidden="1" spans="1:3">
       <c r="A35" s="1" t="s">
         <v>3</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>471140357897623</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" hidden="1" spans="1:3">
       <c r="A36" s="1" t="s">
         <v>3</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>482641962922505</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" hidden="1" spans="1:3">
       <c r="A37" s="1" t="s">
         <v>3</v>
       </c>
@@ -1617,7 +1617,7 @@
         <v>535228068114221</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" hidden="1" spans="1:3">
       <c r="A38" s="1" t="s">
         <v>3</v>
       </c>
@@ -1628,7 +1628,7 @@
         <v>524452672285951</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" hidden="1" spans="1:3">
       <c r="A39" s="1" t="s">
         <v>3</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>529591805195542</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" hidden="1" spans="1:3">
       <c r="A40" s="1" t="s">
         <v>3</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>346539456146216</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" hidden="1" spans="1:3">
       <c r="A41" s="1" t="s">
         <v>3</v>
       </c>
@@ -1661,7 +1661,7 @@
         <v>313473032725328</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" hidden="1" spans="1:3">
       <c r="A42" s="1" t="s">
         <v>3</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>446215689624638</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" hidden="1" spans="1:3">
       <c r="A43" s="1" t="s">
         <v>3</v>
       </c>
@@ -1683,7 +1683,7 @@
         <v>503447028794281</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" hidden="1" spans="1:3">
       <c r="A44" s="1" t="s">
         <v>3</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>366801544664991</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" hidden="1" spans="1:3">
       <c r="A45" s="1" t="s">
         <v>3</v>
       </c>
@@ -1705,7 +1705,7 @@
         <v>425375621021662</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" hidden="1" spans="1:3">
       <c r="A46" s="1" t="s">
         <v>3</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>523799382078044</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" hidden="1" spans="1:3">
       <c r="A47" s="1" t="s">
         <v>3</v>
       </c>
@@ -1727,7 +1727,7 @@
         <v>472801251929220</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" hidden="1" spans="1:3">
       <c r="A48" s="1" t="s">
         <v>3</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>334025882084476</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" hidden="1" spans="1:3">
       <c r="A49" s="1" t="s">
         <v>3</v>
       </c>
@@ -1749,7 +1749,7 @@
         <v>401612231205176</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
+    <row r="50" hidden="1" spans="1:3">
       <c r="A50" s="1" t="s">
         <v>3</v>
       </c>
@@ -1760,7 +1760,7 @@
         <v>308939273312687</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" hidden="1" spans="1:3">
       <c r="A51" s="1" t="s">
         <v>3</v>
       </c>
@@ -1771,7 +1771,7 @@
         <v>401365539976836</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
+    <row r="52" hidden="1" spans="1:3">
       <c r="A52" s="1" t="s">
         <v>3</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>433335613366404</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" hidden="1" spans="1:3">
       <c r="A53" s="1" t="s">
         <v>3</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>441410860036208</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
+    <row r="54" hidden="1" spans="1:3">
       <c r="A54" s="1" t="s">
         <v>3</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>429837066683531</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" hidden="1" spans="1:3">
       <c r="A55" s="1" t="s">
         <v>3</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>539013258524189</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" hidden="1" spans="1:3">
       <c r="A56" s="1" t="s">
         <v>3</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>504569887605341</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" hidden="1" spans="1:3">
       <c r="A57" s="1" t="s">
         <v>3</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>508905339776104</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
+    <row r="58" hidden="1" spans="1:3">
       <c r="A58" s="1" t="s">
         <v>3</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>534335570767023</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" hidden="1" spans="1:3">
       <c r="A59" s="1" t="s">
         <v>3</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>487643471190091</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" hidden="1" spans="1:3">
       <c r="A60" s="1" t="s">
         <v>3</v>
       </c>
@@ -1870,7 +1870,7 @@
         <v>484402725596987</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" hidden="1" spans="1:3">
       <c r="A61" s="1" t="s">
         <v>3</v>
       </c>
@@ -1881,7 +1881,7 @@
         <v>521495228973561</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" hidden="1" spans="1:3">
       <c r="A62" s="1" t="s">
         <v>3</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>519711144359293</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" hidden="1" spans="1:3">
       <c r="A63" s="1" t="s">
         <v>3</v>
       </c>
@@ -1903,7 +1903,7 @@
         <v>332450786228909</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" hidden="1" spans="1:3">
       <c r="A64" s="1" t="s">
         <v>3</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>472306919321337</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" hidden="1" spans="1:3">
       <c r="A65" s="1" t="s">
         <v>3</v>
       </c>
@@ -1925,7 +1925,7 @@
         <v>294510919025493</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" hidden="1" spans="1:3">
       <c r="A66" s="1" t="s">
         <v>3</v>
       </c>
@@ -1936,7 +1936,7 @@
         <v>314198135846951</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
+    <row r="67" hidden="1" spans="1:3">
       <c r="A67" s="1" t="s">
         <v>3</v>
       </c>
@@ -1947,7 +1947,7 @@
         <v>301272899284519</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" hidden="1" spans="1:3">
       <c r="A68" s="1" t="s">
         <v>3</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>557012651492091</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" hidden="1" spans="1:3">
       <c r="A69" s="1" t="s">
         <v>3</v>
       </c>
@@ -1969,7 +1969,7 @@
         <v>321787416213772</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" hidden="1" spans="1:3">
       <c r="A70" s="1" t="s">
         <v>3</v>
       </c>
@@ -1980,7 +1980,7 @@
         <v>356075740286859</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" hidden="1" spans="1:3">
       <c r="A71" s="1" t="s">
         <v>3</v>
       </c>
@@ -1991,7 +1991,7 @@
         <v>482659141675772</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
+    <row r="72" hidden="1" spans="1:3">
       <c r="A72" s="1" t="s">
         <v>3</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>428312681992900</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
+    <row r="73" hidden="1" spans="1:3">
       <c r="A73" s="1" t="s">
         <v>3</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>559692267341435</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" hidden="1" spans="1:3">
       <c r="A74" s="1" t="s">
         <v>3</v>
       </c>
@@ -2024,7 +2024,7 @@
         <v>378350424121337</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" hidden="1" spans="1:3">
       <c r="A75" s="1" t="s">
         <v>3</v>
       </c>
@@ -2035,7 +2035,7 @@
         <v>358005520498533</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" hidden="1" spans="1:3">
       <c r="A76" s="1" t="s">
         <v>3</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>536777664855926</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" hidden="1" spans="1:3">
       <c r="A77" s="1" t="s">
         <v>3</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>353433524103491</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" hidden="1" spans="1:3">
       <c r="A78" s="1" t="s">
         <v>3</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>532860951111430</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" hidden="1" spans="1:3">
       <c r="A79" s="1" t="s">
         <v>3</v>
       </c>
@@ -2079,7 +2079,7 @@
         <v>560892561352907</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" hidden="1" spans="1:3">
       <c r="A80" s="1" t="s">
         <v>3</v>
       </c>
@@ -2090,7 +2090,7 @@
         <v>417913031659956</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" hidden="1" spans="1:3">
       <c r="A81" s="1" t="s">
         <v>3</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>300107079966043</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" hidden="1" spans="1:3">
       <c r="A82" s="1" t="s">
         <v>3</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>455867806046084</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" hidden="1" spans="1:3">
       <c r="A83" s="1" t="s">
         <v>3</v>
       </c>
@@ -2123,7 +2123,7 @@
         <v>320140005453692</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" hidden="1" spans="1:3">
       <c r="A84" s="1" t="s">
         <v>3</v>
       </c>
@@ -2134,7 +2134,7 @@
         <v>465022500020284</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" hidden="1" spans="1:3">
       <c r="A85" s="1" t="s">
         <v>3</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>554841108661119</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" hidden="1" spans="1:3">
       <c r="A86" s="1" t="s">
         <v>3</v>
       </c>
@@ -2156,7 +2156,7 @@
         <v>519978880437107</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" hidden="1" spans="1:3">
       <c r="A87" s="1" t="s">
         <v>3</v>
       </c>
@@ -2167,7 +2167,7 @@
         <v>455830968837164</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" hidden="1" spans="1:3">
       <c r="A88" s="1" t="s">
         <v>3</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>558412369719257</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" hidden="1" spans="1:3">
       <c r="A89" s="1" t="s">
         <v>3</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>288634818568698</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" hidden="1" spans="1:3">
       <c r="A90" s="1" t="s">
         <v>5</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>394649622444477</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" hidden="1" spans="1:3">
       <c r="A91" s="1" t="s">
         <v>5</v>
       </c>
@@ -2211,7 +2211,7 @@
         <v>356968446159933</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" hidden="1" spans="1:3">
       <c r="A92" s="1" t="s">
         <v>5</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>447340814508535</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" hidden="1" spans="1:3">
       <c r="A93" s="1" t="s">
         <v>5</v>
       </c>
@@ -2233,7 +2233,7 @@
         <v>443799381088719</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" hidden="1" spans="1:3">
       <c r="A94" s="1" t="s">
         <v>5</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>520185265872885</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" hidden="1" spans="1:3">
       <c r="A95" s="1" t="s">
         <v>5</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>390491107282087</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" hidden="1" spans="1:3">
       <c r="A96" s="1" t="s">
         <v>5</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>414994478166937</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" hidden="1" spans="1:3">
       <c r="A97" s="1" t="s">
         <v>5</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v>524830424820179</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" hidden="1" spans="1:3">
       <c r="A98" s="1" t="s">
         <v>5</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>464961961308319</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
+    <row r="99" hidden="1" spans="1:3">
       <c r="A99" s="1" t="s">
         <v>5</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>464480407481271</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" hidden="1" spans="1:3">
       <c r="A100" s="1" t="s">
         <v>5</v>
       </c>
@@ -2310,7 +2310,7 @@
         <v>549692190626349</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" hidden="1" spans="1:3">
       <c r="A101" s="1" t="s">
         <v>5</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>444461122633265</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
+    <row r="102" hidden="1" spans="1:3">
       <c r="A102" s="1" t="s">
         <v>5</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>542258471747055</v>
       </c>
     </row>
-    <row r="103" spans="1:3">
+    <row r="103" hidden="1" spans="1:3">
       <c r="A103" s="1" t="s">
         <v>5</v>
       </c>
@@ -2343,7 +2343,7 @@
         <v>291523628478477</v>
       </c>
     </row>
-    <row r="104" spans="1:3">
+    <row r="104" hidden="1" spans="1:3">
       <c r="A104" s="1" t="s">
         <v>5</v>
       </c>
@@ -2354,7 +2354,7 @@
         <v>562333069158959</v>
       </c>
     </row>
-    <row r="105" spans="1:3">
+    <row r="105" hidden="1" spans="1:3">
       <c r="A105" s="1" t="s">
         <v>5</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>526563138342496</v>
       </c>
     </row>
-    <row r="106" spans="1:3">
+    <row r="106" hidden="1" spans="1:3">
       <c r="A106" s="1" t="s">
         <v>5</v>
       </c>
@@ -2376,7 +2376,7 @@
         <v>550065648436187</v>
       </c>
     </row>
-    <row r="107" spans="1:3">
+    <row r="107" hidden="1" spans="1:3">
       <c r="A107" s="1" t="s">
         <v>5</v>
       </c>
@@ -2387,7 +2387,7 @@
         <v>335657172273758</v>
       </c>
     </row>
-    <row r="108" spans="1:3">
+    <row r="108" hidden="1" spans="1:3">
       <c r="A108" s="1" t="s">
         <v>5</v>
       </c>
@@ -2398,7 +2398,7 @@
         <v>522579244412805</v>
       </c>
     </row>
-    <row r="109" spans="1:3">
+    <row r="109" hidden="1" spans="1:3">
       <c r="A109" s="1" t="s">
         <v>5</v>
       </c>
@@ -2409,7 +2409,7 @@
         <v>430695296465505</v>
       </c>
     </row>
-    <row r="110" spans="1:3">
+    <row r="110" hidden="1" spans="1:3">
       <c r="A110" s="1" t="s">
         <v>5</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>467897458159128</v>
       </c>
     </row>
-    <row r="111" spans="1:3">
+    <row r="111" hidden="1" spans="1:3">
       <c r="A111" s="1" t="s">
         <v>5</v>
       </c>
@@ -2431,7 +2431,7 @@
         <v>510592086939464</v>
       </c>
     </row>
-    <row r="112" spans="1:3">
+    <row r="112" hidden="1" spans="1:3">
       <c r="A112" s="1" t="s">
         <v>5</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>331867403017875</v>
       </c>
     </row>
-    <row r="113" spans="1:3">
+    <row r="113" hidden="1" spans="1:3">
       <c r="A113" s="1" t="s">
         <v>5</v>
       </c>
@@ -2453,7 +2453,7 @@
         <v>402775194944990</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
+    <row r="114" hidden="1" spans="1:3">
       <c r="A114" s="1" t="s">
         <v>5</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>405387450210364</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
+    <row r="115" hidden="1" spans="1:3">
       <c r="A115" s="1" t="s">
         <v>5</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>458799955488410</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
+    <row r="116" hidden="1" spans="1:3">
       <c r="A116" s="1" t="s">
         <v>5</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>337048132437219</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
+    <row r="117" hidden="1" spans="1:3">
       <c r="A117" s="1" t="s">
         <v>5</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>328355249059935</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
+    <row r="118" hidden="1" spans="1:3">
       <c r="A118" s="1" t="s">
         <v>5</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>516631322993943</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
+    <row r="119" hidden="1" spans="1:3">
       <c r="A119" s="1" t="s">
         <v>5</v>
       </c>
@@ -2519,7 +2519,7 @@
         <v>360903318858545</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
+    <row r="120" hidden="1" spans="1:3">
       <c r="A120" s="1" t="s">
         <v>5</v>
       </c>
@@ -2530,7 +2530,7 @@
         <v>314385218684213</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
+    <row r="121" hidden="1" spans="1:3">
       <c r="A121" s="1" t="s">
         <v>5</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>377259018242054</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
+    <row r="122" hidden="1" spans="1:3">
       <c r="A122" s="1" t="s">
         <v>5</v>
       </c>
@@ -2554,6 +2554,11 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:C122" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="311366409564048"/>
+      </filters>
+    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
